--- a/stories/arbres/TREE-REL-076.xlsx
+++ b/stories/arbres/TREE-REL-076.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Tom est avec papa, sur le chemin de l'école. Tom a envie de jouer. papa est là, tout près. On va apprendre : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom écoute papa. Tom entend les mots : stop, s'éloigner, maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Tom se souvient : stop, s'éloigner, maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. On attend son tour. papa dit : je suis là. On reste ensemble.</t>
+          <t>Tom va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Tom se souvient : stop, s'éloigner, maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Tom se souvient : stop, s'éloigner, maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. On attend son tour.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Dire stop et rejoindre la maîtresse.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom respire. Tom retient : stop, s'éloigner, maîtresse. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2584,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2751,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. Un chat miaule une fois. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. Les chaussures font toc toc. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. La couverture est douce. On rit un peu. Cette fin-là est celle de la cuisine, les cubes et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3944,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4111,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. Les chaussures font toc toc. On attend son tour. Cette fin-là est celle de la cuisine, le livre et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4278,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4445,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. La couverture est douce. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4612,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4779,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. On entend un oiseau. On rit un peu. Cette fin-là est celle de la cuisine, le livre et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4946,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5113,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5304,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5471,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. La couverture est douce. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5638,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5805,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. On entend un oiseau. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5972,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6139,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de la cuisine, la dînette et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6306,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6335,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Tom se souvient : stop, s'éloigner, maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. On montre du doigt, sans courir. papa dit : je suis là. On reste ensemble.</t>
+          <t>Tom va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Tom se souvient : stop, s'éloigner, maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6473,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Tom se souvient : stop, s'éloigner, maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. On montre du doigt, sans courir.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6659,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Dire stop et rejoindre la maîtresse.</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6832,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom respire. Tom retient : stop, s'éloigner, maîtresse. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7023,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7001,6 +7190,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7381,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7548,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. Les chaussures font toc toc. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7715,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7882,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. La couverture est douce. On rit un peu. Cette fin-là est celle de le jardin, les cubes et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8049,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8216,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de le jardin, les cubes et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8383,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8550,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8741,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8908,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. La couverture est douce. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9075,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9242,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. On entend un oiseau. On rit un peu. Cette fin-là est celle de le jardin, le livre et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9409,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9576,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de le jardin, le livre et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9743,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9910,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10101,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10268,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. On entend un oiseau. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10435,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10602,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le jardin, la dînette et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10769,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10936,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. Le vent est doux. On se tait une seconde. Cette fin-là est celle de le jardin, la dînette et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11103,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10823,7 +11132,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Tom se souvient : stop, s'éloigner, maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. On rit un peu. papa dit : je suis là. On reste ensemble.</t>
+          <t>Tom va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Tom se souvient : stop, s'éloigner, maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10961,6 +11270,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Tom se souvient : stop, s'éloigner, maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. On rit un peu.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11456,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Dire stop et rejoindre la maîtresse.</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11629,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom respire. Tom retient : stop, s'éloigner, maîtresse. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11820,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11987,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12178,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12345,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. La couverture est douce. On rit un peu. Cette fin-là est celle de la chambre, les cubes et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12512,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12679,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12846,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13013,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de la chambre, les cubes et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13180,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13347,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13538,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13325,6 +13705,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. On entend un oiseau. On rit un peu. Cette fin-là est celle de la chambre, le livre et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13872,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14039,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14206,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14373,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. Le vent est doux. On se tient la main. Cette fin-là est celle de la chambre, le livre et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14540,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14707,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14898,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15065,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de la chambre, la dînette et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15232,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15399,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. Le vent est doux. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15566,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15733,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de la chambre, la dînette et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15900,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15490,6 +15940,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-REL-076.xlsx
+++ b/stories/arbres/TREE-REL-076.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Tom est avec papa, sur le chemin de l'école. Tom a envie de jouer. papa est là, tout près. On va apprendre : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom écoute papa. Tom entend les mots : stop, s'éloigner, maîtresse.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Dire stop et rejoindre la maîtresse.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom respire. Tom retient : stop, s'éloigner, maîtresse. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Tom a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Tom rejoint le matin. Un chat miaule une fois. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Tom rejoint après la sieste. Les chaussures font toc toc. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Tom rejoint le soir. La couverture est douce. On rit un peu. Cette fin-là est celle de la cuisine, les cubes et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Tom a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3949,6 +3969,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4116,6 +4137,7 @@
           <t>narrateur|Tom rejoint le matin. Les chaussures font toc toc. On attend son tour. Cette fin-là est celle de la cuisine, le livre et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4283,6 +4305,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4450,6 +4473,7 @@
           <t>narrateur|Tom rejoint après la sieste. La couverture est douce. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4617,6 +4641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4784,6 +4809,7 @@
           <t>narrateur|Tom rejoint le soir. On entend un oiseau. On rit un peu. Cette fin-là est celle de la cuisine, le livre et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4951,6 +4977,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5118,6 +5145,7 @@
           <t>narrateur|Tom a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5309,6 +5337,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5476,6 +5505,7 @@
           <t>narrateur|Tom rejoint le matin. La couverture est douce. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5643,6 +5673,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5810,6 +5841,7 @@
           <t>narrateur|Tom rejoint après la sieste. On entend un oiseau. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5977,6 +6009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6144,6 +6177,7 @@
           <t>narrateur|Tom rejoint le soir. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de la cuisine, la dînette et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6311,6 +6345,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6479,6 +6514,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6666,6 +6702,7 @@
           <t>narrateur|Que fait-on ? Dire stop et rejoindre la maîtresse.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6837,6 +6874,7 @@
           <t>narrateur|Oui. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom respire. Tom retient : stop, s'éloigner, maîtresse. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7028,6 +7066,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7195,6 +7234,7 @@
           <t>narrateur|Tom a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7386,6 +7426,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7553,6 +7594,7 @@
           <t>narrateur|Tom rejoint le matin. Les chaussures font toc toc. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7720,6 +7762,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7887,6 +7930,7 @@
           <t>narrateur|Tom rejoint après la sieste. La couverture est douce. On rit un peu. Cette fin-là est celle de le jardin, les cubes et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8054,6 +8098,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8221,6 +8266,7 @@
           <t>narrateur|Tom rejoint le soir. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de le jardin, les cubes et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8388,6 +8434,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8555,6 +8602,7 @@
           <t>narrateur|Tom a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8746,6 +8794,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8913,6 +8962,7 @@
           <t>narrateur|Tom rejoint le matin. La couverture est douce. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9080,6 +9130,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9247,6 +9298,7 @@
           <t>narrateur|Tom rejoint après la sieste. On entend un oiseau. On rit un peu. Cette fin-là est celle de le jardin, le livre et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9414,6 +9466,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9581,6 +9634,7 @@
           <t>narrateur|Tom rejoint le soir. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de le jardin, le livre et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9748,6 +9802,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9915,6 +9970,7 @@
           <t>narrateur|Tom a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10106,6 +10162,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10273,6 +10330,7 @@
           <t>narrateur|Tom rejoint le matin. On entend un oiseau. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10440,6 +10498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10607,6 +10666,7 @@
           <t>narrateur|Tom rejoint après la sieste. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le jardin, la dînette et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10774,6 +10834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10941,6 +11002,7 @@
           <t>narrateur|Tom rejoint le soir. Le vent est doux. On se tait une seconde. Cette fin-là est celle de le jardin, la dînette et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11108,6 +11170,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11276,6 +11339,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11463,6 +11527,7 @@
           <t>narrateur|Que fait-on ? Dire stop et rejoindre la maîtresse.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11634,6 +11699,7 @@
           <t>narrateur|Oui. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom respire. Tom retient : stop, s'éloigner, maîtresse. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11825,6 +11891,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11992,6 +12059,7 @@
           <t>narrateur|Tom a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12183,6 +12251,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12350,6 +12419,7 @@
           <t>narrateur|Tom rejoint le matin. La couverture est douce. On rit un peu. Cette fin-là est celle de la chambre, les cubes et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12517,6 +12587,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12684,6 +12755,7 @@
           <t>narrateur|Tom rejoint après la sieste. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12851,6 +12923,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13018,6 +13091,7 @@
           <t>narrateur|Tom rejoint le soir. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de la chambre, les cubes et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13185,6 +13259,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13352,6 +13427,7 @@
           <t>narrateur|Tom a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13543,6 +13619,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13710,6 +13787,7 @@
           <t>narrateur|Tom rejoint le matin. On entend un oiseau. On rit un peu. Cette fin-là est celle de la chambre, le livre et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13877,6 +13955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14044,6 +14123,7 @@
           <t>narrateur|Tom rejoint après la sieste. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14211,6 +14291,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14378,6 +14459,7 @@
           <t>narrateur|Tom rejoint le soir. Le vent est doux. On se tient la main. Cette fin-là est celle de la chambre, le livre et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14545,6 +14627,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14712,6 +14795,7 @@
           <t>narrateur|Tom a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom répète tout bas : stop, s'éloigner, maîtresse. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14903,6 +14987,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15070,6 +15155,7 @@
           <t>narrateur|Tom rejoint le matin. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de la chambre, la dînette et le matin. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15237,6 +15323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15404,6 +15491,7 @@
           <t>narrateur|Tom rejoint après la sieste. Le vent est doux. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et après la sieste. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15571,6 +15659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15738,6 +15827,7 @@
           <t>narrateur|Tom rejoint le soir. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de la chambre, la dînette et le soir. Tom a appris : Dire stop et rejoindre la maîtresse. Voici le geste : dire stop ; s'éloigner ; aller vers la maîtresse. Tom a entendu : stop, s'éloigner, maîtresse. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15905,6 +15995,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15923,7 +16014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15947,6 +16038,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15961,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16148,6 +16253,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
